--- a/Stat101/datasets/New folder/Stat101Project.xlsx
+++ b/Stat101/datasets/New folder/Stat101Project.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkill\Documents\GitHub\school\Stat101\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkill\Documents\GitHub\school\Stat101\datasets\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EE83D13-F38B-466A-B324-A4DBD01E8D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1A5B62-761E-4E8F-BFF2-D0DE7C5CC906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataSheet" sheetId="1" r:id="rId1"/>
     <sheet name="CPI Per Year" sheetId="2" r:id="rId2"/>
+    <sheet name="CPI Stat Charts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -143,8 +144,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="#0.0"/>
-    <numFmt numFmtId="170" formatCode="#0.000"/>
+    <numFmt numFmtId="164" formatCode="#0.0"/>
+    <numFmt numFmtId="165" formatCode="#0.000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -271,14 +272,23 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -292,15 +302,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -317,6 +318,9541 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CPI Per Year'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Standard Deviation</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$A$2:$A$1048576</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$E$2:$E$52</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$E$3:$E$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>0.9238834374858157</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1453132428477479</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.790547571571504</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7637671918794289</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6137602078695785</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4484224977059679</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5521246435421716</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3232192149863491</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2194136693385442</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.195699364262174</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64308677957225002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.5100421426990964</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7233468143192308</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6516291314574205</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3403412079645523</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.183568051838735</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3085962870283001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0439943689619451</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2329749684106635</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0953067925001458</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3774152341515347</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.78257539088847217</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.82402375664488781</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.446704719510705</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.7246870598880948</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.95663551844551398</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3578894050561103</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.93658794018339386</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.8264886000357685</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.6210540327174185</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.8022502769055306</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.4348452053965222</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.4660044457821728</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.8123586841461594</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.75509150559265148</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.1531681027703948</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.3536880571463319</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.015793864050391</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.5304604674490079</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.5579432245460973</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.7322112422792995</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.3377403918775157</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.5496843569129173</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.8158875344797099</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.4977135806611812</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.809153061802947</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.870240500855032</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.8673805105748014</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.2707621801474267</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.1357339278838765</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5B1B-45DB-B694-8D7C546ABBCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="215108255"/>
+        <c:axId val="215105375"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mean</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$B$2:$B$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$3:$B$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>56.908333333333339</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>60.608333333333327</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>65.233333333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>72.575000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.408333333333317</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>90.924999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>96.5</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>99.600000000000009</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>103.88333333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>107.56666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.60833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>113.625</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>118.25833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>123.96666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>130.65833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>136.19166666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>140.31666666666669</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.45833333333331</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>148.22500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.38333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>156.84999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>160.51666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>163.00833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.57500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.19999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.06666666666663</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>179.875</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>183.95833333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>188.88333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>195.29166666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.5916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>207.34241666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>215.30250000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>214.53700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.05550000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>224.93916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.5939166666667</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>232.95708333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>236.73616666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.01700000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>240.00716666666662</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>245.11958333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>251.10683333333338</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>255.65741666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>258.81116666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>270.96975000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>292.65491666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>304.7015833333333</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>313.68883333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>321.04962499999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-5B1B-45DB-B694-8D7C546ABBCB}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Median</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$C$2:$C$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$3:$C$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>56.95</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>60.85</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>65.45</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>72.699999999999989</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>91.1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>97.25</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>99.7</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>103.9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>107.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.55</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>113.65</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>118.25</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>124.25</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>130.15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>136.1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>140.35</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>148.19999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>156.85</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>160.4</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>163.1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.45</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.45</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>180</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>184.05</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>189.45</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>195</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.8</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>208.12400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>215.69800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>215.52199999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.09449999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>225.822</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.708</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>233.059</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>237.2525</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.57050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>240.73849999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>244.87049999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>251.7885</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>256.35050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>258.8895</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>272.34950000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>296.2235</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>305.39999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>314.35750000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>321.13</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-5B1B-45DB-B694-8D7C546ABBCB}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mode</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$D$2:$D$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$3:$D$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>97.9</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>105.3</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.5</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>115.4</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>133.80000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>149.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>158.6</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>164</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.2</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.8</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.7</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>179.8</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.5</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-5B1B-45DB-B694-8D7C546ABBCB}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="215108255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215105375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="215105375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215108255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CPI Per Year'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mean</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>'CPI Per Year'!$A:$A</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CPI Per Year'!$B$2:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>53.81666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56.908333333333339</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60.608333333333327</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.233333333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72.575000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82.408333333333317</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>90.924999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>96.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99.600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>103.88333333333333</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>107.56666666666665</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>109.60833333333335</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>113.625</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>118.25833333333333</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>123.96666666666665</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>130.65833333333333</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>136.19166666666666</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>140.31666666666669</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>144.45833333333331</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>148.22500000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>152.38333333333335</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>156.84999999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>160.51666666666665</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>163.00833333333335</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>166.57500000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>172.19999999999996</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>177.06666666666663</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>179.875</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>183.95833333333334</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>188.88333333333335</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>195.29166666666671</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>201.5916666666667</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>207.34241666666671</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>215.30250000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>214.53700000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>218.05550000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>224.93916666666667</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>229.5939166666667</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>232.95708333333332</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>236.73616666666666</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>237.01700000000002</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>240.00716666666662</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>245.11958333333334</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>251.10683333333338</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>255.65741666666668</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>258.81116666666668</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>270.96975000000003</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>292.65491666666668</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>304.7015833333333</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>313.68883333333332</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>321.04962499999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-38E8-47A8-9621-A8607660B644}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="215108255"/>
+        <c:axId val="215105375"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Median</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="25400" cap="rnd">
+                    <a:noFill/>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="52"/>
+                      <c:pt idx="0">
+                        <c:v>Year</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$2:$C$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>53.900000000000006</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>56.95</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>60.85</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>65.45</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>72.699999999999989</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>91.1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>97.25</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>99.7</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>103.9</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>107.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>109.55</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>113.65</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>118.25</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>124.25</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>130.15</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>136.1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>140.35</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>148.19999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>156.85</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>160.4</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>163.1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>166.45</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>172.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>177.45</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>180</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>184.05</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>189.45</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>195</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>201.8</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>208.12400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>215.69800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>215.52199999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>218.09449999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>225.822</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>229.708</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>233.059</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.2525</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>237.57050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>240.73849999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>244.87049999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>251.7885</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>256.35050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>258.8895</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>272.34950000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>296.2235</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>305.39999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>314.35750000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>321.13</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-38E8-47A8-9621-A8607660B644}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mode</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="25400" cap="rnd">
+                    <a:noFill/>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="52"/>
+                      <c:pt idx="0">
+                        <c:v>Year</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$2:$D$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>97.9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>105.3</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>109.5</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>115.4</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>133.80000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>149.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>158.6</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>164</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>166.2</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>172.8</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>177.7</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>179.8</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>201.5</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-38E8-47A8-9621-A8607660B644}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Standard Deviation</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="25400" cap="rnd">
+                    <a:noFill/>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="52"/>
+                      <c:pt idx="0">
+                        <c:v>Year</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$2:$E$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1.1440226740707009</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.9238834374858157</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1.1453132428477479</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1.790547571571504</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2.7637671918794289</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2.6137602078695785</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2.4484224977059679</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.5521246435421716</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1.3232192149863491</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1.2194136693385442</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1.195699364262174</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>0.64308677957225002</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.5100421426990964</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.7233468143192308</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1.6516291314574205</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2.3403412079645523</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.183568051838735</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1.3085962870283001</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1.0439943689619451</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.2329749684106635</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.0953067925001458</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1.3774152341515347</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>0.78257539088847217</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>0.82402375664488781</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.446704719510705</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.7246870598880948</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>0.95663551844551398</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.3578894050561103</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>0.93658794018339386</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.8264886000357685</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2.6210540327174185</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.8022502769055306</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2.4348452053965222</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>3.4660044457821728</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1.8123586841461594</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>0.75509150559265148</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2.1531681027703948</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1.3536880571463319</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1.015793864050391</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1.5304604674490079</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1.5579432245460973</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1.7322112422792995</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1.3377403918775157</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>1.5496843569129173</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>1.8158875344797099</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>1.4977135806611812</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>5.809153061802947</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>5.870240500855032</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2.8673805105748014</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2.2707621801474267</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2.1357339278838765</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-38E8-47A8-9621-A8607660B644}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="215108255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215105375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="215105375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215108255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CPI Per Year'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Median</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$A$2:$A$1048576</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$C$2:$C$52</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$C$3:$C$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>56.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.699999999999989</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>91.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>97.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>103.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>107.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>109.55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>113.65</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>118.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>124.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>130.15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>136.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>140.35</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>144.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>148.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>152.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>156.85</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>160.4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>163.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>166.45</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>172.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>177.45</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>184.05</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>189.45</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>201.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>208.12400000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>215.69800000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>215.52199999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>218.09449999999998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>225.822</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>229.708</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>233.059</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>237.2525</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>237.57050000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>240.73849999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>244.87049999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>251.7885</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>256.35050000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>258.8895</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>272.34950000000003</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>296.2235</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>305.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>314.35750000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>321.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-40E4-41F8-B34F-D909EF090BF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="215108255"/>
+        <c:axId val="215105375"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mean</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$B$2:$B$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$3:$B$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>56.908333333333339</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>60.608333333333327</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>65.233333333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>72.575000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.408333333333317</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>90.924999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>96.5</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>99.600000000000009</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>103.88333333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>107.56666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.60833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>113.625</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>118.25833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>123.96666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>130.65833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>136.19166666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>140.31666666666669</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.45833333333331</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>148.22500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.38333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>156.84999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>160.51666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>163.00833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.57500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.19999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.06666666666663</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>179.875</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>183.95833333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>188.88333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>195.29166666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.5916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>207.34241666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>215.30250000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>214.53700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.05550000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>224.93916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.5939166666667</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>232.95708333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>236.73616666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.01700000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>240.00716666666662</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>245.11958333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>251.10683333333338</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>255.65741666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>258.81116666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>270.96975000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>292.65491666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>304.7015833333333</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>313.68883333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>321.04962499999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-40E4-41F8-B34F-D909EF090BF4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mode</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$D$2:$D$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$D$3:$D$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>97.9</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>105.3</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.5</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>115.4</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>133.80000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>149.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>158.6</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>164</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.2</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.8</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.7</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>179.8</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.5</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>#N/A</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-40E4-41F8-B34F-D909EF090BF4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Standard Deviation</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent5"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$E$2:$E$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$3:$E$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>0.9238834374858157</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1.1453132428477479</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1.790547571571504</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2.7637671918794289</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2.6137602078695785</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2.4484224977059679</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1.5521246435421716</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.3232192149863491</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1.2194136693385442</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1.195699364262174</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.64308677957225002</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1.5100421426990964</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.7233468143192308</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.6516291314574205</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2.3403412079645523</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1.183568051838735</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.3085962870283001</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1.0439943689619451</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1.2329749684106635</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.0953067925001458</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.3774152341515347</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.78257539088847217</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>0.82402375664488781</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.446704719510705</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.7246870598880948</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>0.95663551844551398</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.3578894050561103</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.93658794018339386</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.8264886000357685</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2.6210540327174185</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.8022502769055306</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2.4348452053965222</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>3.4660044457821728</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.8123586841461594</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>0.75509150559265148</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2.1531681027703948</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>1.3536880571463319</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1.015793864050391</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1.5304604674490079</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1.5579432245460973</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1.7322112422792995</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1.3377403918775157</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1.5496843569129173</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>1.8158875344797099</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>1.4977135806611812</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>5.809153061802947</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>5.870240500855032</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2.8673805105748014</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2.2707621801474267</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2.1357339278838765</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-40E4-41F8-B34F-D909EF090BF4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="215108255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215105375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="215105375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215108255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CPI Per Year'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mode</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$A$2:$A$1048576</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'CPI Per Year'!$D$2:$D$52</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'CPI Per Year'!$D$3:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>105.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>109.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>115.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>133.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>144.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>149.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>152.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>158.6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>166.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>172.8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>177.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>179.8</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>201.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6D9A-4CEF-BACC-1A229C2B7642}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="215108255"/>
+        <c:axId val="215105375"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Mean</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$B$2:$B$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$B$3:$B$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>56.908333333333339</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>60.608333333333327</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>65.233333333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>72.575000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.408333333333317</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>90.924999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>96.5</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>99.600000000000009</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>103.88333333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>107.56666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.60833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>113.625</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>118.25833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>123.96666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>130.65833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>136.19166666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>140.31666666666669</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.45833333333331</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>148.22500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.38333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>156.84999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>160.51666666666665</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>163.00833333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.57500000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.19999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.06666666666663</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>179.875</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>183.95833333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>188.88333333333335</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>195.29166666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.5916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>207.34241666666671</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>215.30250000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>214.53700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.05550000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>224.93916666666667</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.5939166666667</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>232.95708333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>236.73616666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.01700000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>240.00716666666662</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>245.11958333333334</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>251.10683333333338</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>255.65741666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>258.81116666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>270.96975000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>292.65491666666668</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>304.7015833333333</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>313.68883333333332</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>321.04962499999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-6D9A-4CEF-BACC-1A229C2B7642}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Median</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$C$2:$C$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$C$3:$C$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>56.95</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>60.85</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>65.45</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>72.699999999999989</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>82.7</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>91.1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>97.25</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>99.7</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>103.9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>107.69999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>109.55</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>113.65</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>118.25</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>124.25</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>130.15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>136.1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>140.35</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>144.4</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>148.19999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>152.5</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>156.85</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>160.4</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>163.1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>166.45</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>172.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>177.45</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>180</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>184.05</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>189.45</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>195</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>201.8</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>208.12400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>215.69800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>215.52199999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.09449999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>225.822</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.708</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>233.059</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>237.2525</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>237.57050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>240.73849999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>244.87049999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>251.7885</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>256.35050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>258.8895</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>272.34950000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>296.2235</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>305.39999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>314.35750000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>321.13</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-6D9A-4CEF-BACC-1A229C2B7642}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Standard Deviation</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$A:$A</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$A$2:$A$1048576</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="51"/>
+                      <c:pt idx="0">
+                        <c:v>1975</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1976</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1977</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1978</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1979</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1980</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>2016</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>2017</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'CPI Per Year'!$E$2:$E$52</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'CPI Per Year'!$E$3:$E$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="50"/>
+                      <c:pt idx="0">
+                        <c:v>0.9238834374858157</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1.1453132428477479</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1.790547571571504</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2.7637671918794289</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2.6137602078695785</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2.4484224977059679</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1.5521246435421716</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.3232192149863491</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1.2194136693385442</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1.195699364262174</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.64308677957225002</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1.5100421426990964</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.7233468143192308</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.6516291314574205</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2.3403412079645523</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1.183568051838735</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.3085962870283001</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1.0439943689619451</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1.2329749684106635</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.0953067925001458</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.3774152341515347</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.78257539088847217</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>0.82402375664488781</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.446704719510705</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.7246870598880948</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>0.95663551844551398</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.3578894050561103</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.93658794018339386</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.8264886000357685</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2.6210540327174185</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.8022502769055306</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>2.4348452053965222</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>3.4660044457821728</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.8123586841461594</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>0.75509150559265148</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>2.1531681027703948</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>1.3536880571463319</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1.015793864050391</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1.5304604674490079</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1.5579432245460973</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1.7322112422792995</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1.3377403918775157</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1.5496843569129173</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>1.8158875344797099</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>1.4977135806611812</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>5.809153061802947</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>5.870240500855032</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2.8673805105748014</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2.2707621801474267</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2.1357339278838765</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-6D9A-4CEF-BACC-1A229C2B7642}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="215108255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215105375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="215105375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="215108255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>328222</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>101490</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>172345</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>44900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EC5704F-807B-EA3E-E218-05F2752CADA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>319033</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>65256</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>161204</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6714</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030C0959-FD0C-4199-8822-8774D23CB833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>63026</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>91473</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>516493</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>34882</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FA29FA-AC19-42E5-BCED-EA01E076E01C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>309565</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>81556</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>492671</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>131378</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82B80D25-3A4C-4D9D-B45D-08BED0A9E51A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -644,114 +10180,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -3163,19 +12699,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4255,7 +13791,25 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39D390-DC9C-4806-BFEB-094BB18AB24B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6b32e734-4d8f-4e84-9211-96864bfbbc0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002E0A2A810F25F848BFA092BBEA850C3A" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2279ea7da08e92911f88c4cc3faf736">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6b32e734-4d8f-4e84-9211-96864bfbbc0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="966b50d4ad832fec78d5b075e2dde282" ns3:_="">
     <xsd:import namespace="6b32e734-4d8f-4e84-9211-96864bfbbc0c"/>
@@ -4411,7 +13965,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4420,15 +13974,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6b32e734-4d8f-4e84-9211-96864bfbbc0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C24D654-130C-49AD-BA6B-D96EF66A7F0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="6b32e734-4d8f-4e84-9211-96864bfbbc0c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88BADB8B-209E-43F3-AD16-FDB11FA88310}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4446,26 +14008,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{807C24AE-BA3C-4B17-A19D-B7B1FB48B64B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C24D654-130C-49AD-BA6B-D96EF66A7F0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6b32e734-4d8f-4e84-9211-96864bfbbc0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>